--- a/output/pdf_financials_xlsx/CAI.xlsx
+++ b/output/pdf_financials_xlsx/CAI.xlsx
@@ -888,31 +888,31 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002646</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004493</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000557</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.115282</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003652</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.020892</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.032416</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.037607</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.022941</v>
       </c>
     </row>
     <row r="13">
@@ -1597,31 +1597,31 @@
         <v>-0.782267</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.765066</v>
+        <v>-1.767712</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.952426</v>
+        <v>-0.956919</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.925194</v>
+        <v>-0.925751</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.049711</v>
+        <v>-2.164993</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.714153</v>
+        <v>-1.717805</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.500873</v>
+        <v>-0.521765</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.022819</v>
+        <v>-1.055235</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.380505</v>
+        <v>-0.418112</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.315736</v>
+        <v>0.292795</v>
       </c>
     </row>
     <row r="28">
@@ -1683,31 +1683,31 @@
         <v>-0.688649</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.609617</v>
+        <v>-1.612263</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.803721</v>
+        <v>-0.808214</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.801599</v>
+        <v>-0.802156</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.02857</v>
+        <v>-2.143852</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.523372</v>
+        <v>-1.527024</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.317285</v>
+        <v>-0.338177</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.86994</v>
+        <v>-0.902356</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.20157</v>
+        <v>-0.239177</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.448452</v>
+        <v>0.425511</v>
       </c>
     </row>
     <row r="30">
@@ -1726,13 +1726,13 @@
         <v>-179.2941219352806</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-262.7825993260716</v>
+        <v>-263.2145795784029</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-149.9977604502988</v>
+        <v>-150.836285184259</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-193.8209813408386</v>
+        <v>-193.955660010107</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -1883,13 +1883,13 @@
         <v>0.01663</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.01663</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.406465</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.6024929999999999</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -1897,22 +1897,22 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.118324</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.997996</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.652783</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.893194</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.810621</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.307914</v>
       </c>
     </row>
     <row r="35">
@@ -1973,13 +1973,13 @@
         <v>0.01663</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.01663</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.406465</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.6024929999999999</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -1987,22 +1987,22 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.118324</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.997996</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.652783</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.893194</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.810621</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.307914</v>
       </c>
     </row>
     <row r="37">
@@ -2513,13 +2513,13 @@
         <v>0.027803</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.044433</v>
+        <v>0.027803</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.745945</v>
+        <v>0.33948</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.672948</v>
+        <v>0.070455</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -2527,22 +2527,22 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>9.475666</v>
+        <v>8.357341999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8.998255</v>
+        <v>7.000259</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>9.085672000000001</v>
+        <v>7.432889</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>8.349439</v>
+        <v>7.456245</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.919403</v>
+        <v>0.108782</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.356243</v>
+        <v>0.048329</v>
       </c>
     </row>
     <row r="49">
@@ -5950,19 +5950,19 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.104947</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.133782</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.147538</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.200071</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.158815</v>
       </c>
     </row>
     <row r="125">
@@ -5993,19 +5993,19 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.104947</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.133782</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.147538</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.200071</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.158815</v>
       </c>
     </row>
     <row r="126">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -14696,7 +14696,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -16602,7 +16606,11 @@
           <t>Lease payments (Note 8)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -23280,7 +23288,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -26928,7 +26936,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -27758,7 +27766,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -29864,7 +29872,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E313" s="5" t="n">

--- a/output/pdf_financials_xlsx/CAI.xlsx
+++ b/output/pdf_financials_xlsx/CAI.xlsx
@@ -5432,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.07455000000000001</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -16916,7 +16916,11 @@
           <t>Proceeds from disposition of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -20366,7 +20370,11 @@
           <t>Issuance of common shares, net of issue costs 2,631,500</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
